--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueruifang/Desktop/手搓我的Sims世界/sims-files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A212FAB4-3EA6-A54D-8A98-09D3C644506B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8354D9D-4B65-DE46-9552-205DC9957E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueruifang/Desktop/手搓我的Sims世界/sims-files/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF21845-6D7F-994D-8727-C672E9153286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C476E5AB-435F-D243-BF24-23AE6F850A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17300" yWindow="760" windowWidth="17720" windowHeight="18880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueruifang/Desktop/手搓我的Sims世界/sims-files/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C476E5AB-435F-D243-BF24-23AE6F850A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33260D8-B8F4-764C-AF50-DE12AC84E422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17300" yWindow="760" windowWidth="17720" windowHeight="18880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14150" uniqueCount="6674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14151" uniqueCount="6675">
   <si>
     <t>id</t>
   </si>
@@ -20068,6 +20068,9 @@
   </si>
   <si>
     <t>https://www.curseforge.com/sims4/mods/no-child-messes-only-toddlers</t>
+  </si>
+  <si>
+    <t>https://www.abonnie.uk/starlight-accolades-notification</t>
   </si>
 </sst>
 </file>
@@ -20221,7 +20224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -20247,6 +20250,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1"/>
@@ -57501,10 +57505,10 @@
       <c r="D3" s="1" t="s">
         <v>5616</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="26" t="s">
         <v>5624</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -57525,10 +57529,10 @@
       <c r="D4" s="1" t="s">
         <v>5616</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="26" t="s">
         <v>4882</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="26" t="s">
         <v>5618</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -57694,7 +57698,7 @@
       <c r="G10" s="1" t="s">
         <v>6391</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="16" t="s">
         <v>6346</v>
       </c>
     </row>
@@ -58060,10 +58064,10 @@
       <c r="D24" s="1" t="s">
         <v>5636</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="26" t="s">
         <v>4881</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="26" t="s">
         <v>5278</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -58173,34 +58177,34 @@
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="23" t="s">
         <v>6397</v>
       </c>
-      <c r="B29" s="22" t="str">
+      <c r="B29" s="23" t="str">
         <f>SUBSTITUTE(TRIM(D29)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C29)," ","")</f>
         <v>Alisrabbo_RoastMarshmallowsTogether</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="23" t="s">
         <v>6396</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="23" t="s">
         <v>6394</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="23" t="s">
         <v>4551</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="23" t="s">
         <v>4375</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="23" t="s">
         <v>6348</v>
       </c>
-      <c r="H29" s="29" t="s">
+      <c r="H29" s="30" t="s">
         <v>6398</v>
       </c>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
@@ -58449,10 +58453,10 @@
       <c r="D39" s="1" t="s">
         <v>4398</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="20" t="s">
         <v>4550</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="20" t="s">
         <v>4534</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -58500,10 +58504,10 @@
       <c r="D41" s="1" t="s">
         <v>5218</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="20" t="s">
         <v>4552</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="F41" s="20" t="s">
         <v>4379</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -58626,10 +58630,10 @@
       <c r="D46" s="1" t="s">
         <v>4406</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="22" t="s">
         <v>4456</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="22" t="s">
         <v>4547</v>
       </c>
       <c r="G46" s="7" t="s">
@@ -58653,10 +58657,10 @@
       <c r="D47" s="1" t="s">
         <v>4400</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="21" t="s">
         <v>4550</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="21" t="s">
         <v>4534</v>
       </c>
       <c r="G47" s="7" t="s">
@@ -58680,10 +58684,10 @@
       <c r="D48" s="1" t="s">
         <v>4400</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="E48" s="22" t="s">
         <v>4550</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="22" t="s">
         <v>4685</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -58704,10 +58708,10 @@
       <c r="D49" s="1" t="s">
         <v>4400</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="21" t="s">
         <v>4550</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="21" t="s">
         <v>4534</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -58740,7 +58744,7 @@
       <c r="G50" s="1" t="s">
         <v>6673</v>
       </c>
-      <c r="H50" s="17" t="s">
+      <c r="H50" s="18" t="s">
         <v>5676</v>
       </c>
       <c r="I50" s="14"/>
@@ -58761,10 +58765,10 @@
       <c r="D51" s="1" t="s">
         <v>4400</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="22" t="s">
         <v>4551</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="22" t="s">
         <v>4931</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -58789,10 +58793,10 @@
       <c r="D52" s="14" t="s">
         <v>5687</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="21" t="s">
         <v>4550</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="21" t="s">
         <v>4534</v>
       </c>
       <c r="G52" s="14" t="s">
@@ -58871,10 +58875,10 @@
       <c r="D55" s="1" t="s">
         <v>5068</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="22" t="s">
         <v>4550</v>
       </c>
-      <c r="F55" s="21" t="s">
+      <c r="F55" s="22" t="s">
         <v>5045</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -58898,10 +58902,10 @@
       <c r="D56" s="1" t="s">
         <v>4420</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="21" t="s">
         <v>4550</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" s="21" t="s">
         <v>4534</v>
       </c>
       <c r="G56" s="7" t="s">
@@ -59033,10 +59037,10 @@
       <c r="D61" s="1" t="s">
         <v>4420</v>
       </c>
-      <c r="E61" s="21" t="s">
+      <c r="E61" s="22" t="s">
         <v>4550</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="22" t="s">
         <v>4685</v>
       </c>
       <c r="G61" s="7" t="s">
@@ -59060,10 +59064,10 @@
       <c r="D62" s="1" t="s">
         <v>4420</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="21" t="s">
         <v>4550</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="21" t="s">
         <v>4534</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -59418,7 +59422,7 @@
         <v>4452</v>
       </c>
     </row>
-    <row r="76" spans="1:11" s="22" customFormat="1">
+    <row r="76" spans="1:11" s="23" customFormat="1">
       <c r="A76" s="1" t="s">
         <v>6502</v>
       </c>
@@ -59438,7 +59442,7 @@
       <c r="F76" s="1" t="s">
         <v>6450</v>
       </c>
-      <c r="G76" s="15" t="s">
+      <c r="G76" s="16" t="s">
         <v>6386</v>
       </c>
       <c r="H76" s="1"/>
@@ -59589,13 +59593,13 @@
       <c r="D82" s="14" t="s">
         <v>5717</v>
       </c>
-      <c r="E82" s="25" t="s">
+      <c r="E82" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F82" s="25" t="s">
+      <c r="F82" s="26" t="s">
         <v>4886</v>
       </c>
-      <c r="G82" s="17" t="s">
+      <c r="G82" s="18" t="s">
         <v>5716</v>
       </c>
       <c r="H82" s="14"/>
@@ -59644,7 +59648,7 @@
       <c r="C84" s="1" t="s">
         <v>6404</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="16" t="s">
         <v>6405</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -59653,7 +59657,7 @@
       <c r="F84" s="1" t="s">
         <v>4893</v>
       </c>
-      <c r="G84" s="15" t="s">
+      <c r="G84" s="16" t="s">
         <v>6351</v>
       </c>
     </row>
@@ -60140,7 +60144,7 @@
         <v>5751</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="22" customFormat="1">
+    <row r="104" spans="1:11" s="23" customFormat="1">
       <c r="A104" s="1" t="s">
         <v>5759</v>
       </c>
@@ -60582,34 +60586,34 @@
       </c>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="18" t="s">
+      <c r="A121" s="19" t="s">
         <v>6596</v>
       </c>
-      <c r="B121" s="18" t="str">
+      <c r="B121" s="19" t="str">
         <f>SUBSTITUTE(TRIM(D121)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C121)," ","")</f>
         <v>Ggothichamlet_PlayTogetherBillysBand</v>
       </c>
-      <c r="C121" s="18" t="s">
+      <c r="C121" s="19" t="s">
         <v>4496</v>
       </c>
-      <c r="D121" s="18" t="s">
+      <c r="D121" s="19" t="s">
         <v>6587</v>
       </c>
-      <c r="E121" s="18" t="s">
+      <c r="E121" s="19" t="s">
         <v>4552</v>
       </c>
-      <c r="F121" s="18" t="s">
+      <c r="F121" s="19" t="s">
         <v>4540</v>
       </c>
-      <c r="G121" s="15" t="s">
+      <c r="G121" s="16" t="s">
         <v>4495</v>
       </c>
-      <c r="H121" s="15" t="s">
+      <c r="H121" s="16" t="s">
         <v>4494</v>
       </c>
-      <c r="I121" s="18"/>
-      <c r="J121" s="18"/>
-      <c r="K121" s="18"/>
+      <c r="I121" s="19"/>
+      <c r="J121" s="19"/>
+      <c r="K121" s="19"/>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="1" t="s">
@@ -61349,10 +61353,10 @@
       <c r="D149" s="1" t="s">
         <v>5285</v>
       </c>
-      <c r="E149" s="25" t="s">
+      <c r="E149" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F149" s="25" t="s">
+      <c r="F149" s="26" t="s">
         <v>4886</v>
       </c>
       <c r="G149" s="1" t="s">
@@ -61734,7 +61738,7 @@
         <v>5817</v>
       </c>
     </row>
-    <row r="164" spans="1:11" s="22" customFormat="1">
+    <row r="164" spans="1:11" s="23" customFormat="1">
       <c r="A164" s="1" t="s">
         <v>6533</v>
       </c>
@@ -61952,7 +61956,7 @@
       <c r="G171" s="14" t="s">
         <v>5124</v>
       </c>
-      <c r="H171" s="17" t="s">
+      <c r="H171" s="18" t="s">
         <v>5123</v>
       </c>
       <c r="I171" s="14"/>
@@ -62801,7 +62805,7 @@
       <c r="C203" s="1" t="s">
         <v>6410</v>
       </c>
-      <c r="D203" s="15" t="s">
+      <c r="D203" s="16" t="s">
         <v>5324</v>
       </c>
       <c r="E203" s="1" t="s">
@@ -63500,10 +63504,10 @@
       <c r="D231" s="1" t="s">
         <v>4688</v>
       </c>
-      <c r="E231" s="25" t="s">
+      <c r="E231" s="26" t="s">
         <v>4882</v>
       </c>
-      <c r="F231" s="25" t="s">
+      <c r="F231" s="26" t="s">
         <v>5424</v>
       </c>
       <c r="G231" s="1" t="s">
@@ -64049,7 +64053,7 @@
       <c r="G252" s="14" t="s">
         <v>5175</v>
       </c>
-      <c r="H252" s="17" t="s">
+      <c r="H252" s="18" t="s">
         <v>5174</v>
       </c>
       <c r="I252" s="14"/>
@@ -64175,10 +64179,10 @@
       <c r="D257" s="1" t="s">
         <v>4667</v>
       </c>
-      <c r="E257" s="25" t="s">
+      <c r="E257" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F257" s="25" t="s">
+      <c r="F257" s="26" t="s">
         <v>4532</v>
       </c>
       <c r="G257" s="1" t="s">
@@ -65299,7 +65303,7 @@
         <v>4721</v>
       </c>
     </row>
-    <row r="301" spans="1:11" s="22" customFormat="1">
+    <row r="301" spans="1:11" s="23" customFormat="1">
       <c r="A301" s="1" t="s">
         <v>6578</v>
       </c>
@@ -65519,7 +65523,7 @@
         <v>5983</v>
       </c>
     </row>
-    <row r="310" spans="1:11" s="22" customFormat="1">
+    <row r="310" spans="1:11" s="23" customFormat="1">
       <c r="A310" s="1" t="s">
         <v>5366</v>
       </c>
@@ -66092,7 +66096,7 @@
         <v>6021</v>
       </c>
     </row>
-    <row r="332" spans="1:11" s="18" customFormat="1">
+    <row r="332" spans="1:11" s="19" customFormat="1">
       <c r="A332" s="1" t="s">
         <v>6586</v>
       </c>
@@ -67348,27 +67352,27 @@
         <v>5423</v>
       </c>
     </row>
-    <row r="381" spans="1:11" s="18" customFormat="1">
-      <c r="A381" s="18" t="s">
+    <row r="381" spans="1:11" s="19" customFormat="1">
+      <c r="A381" s="19" t="s">
         <v>6616</v>
       </c>
-      <c r="B381" s="18" t="str">
+      <c r="B381" s="19" t="str">
         <f>SUBSTITUTE(TRIM(D381)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C381)," ","")</f>
         <v>Sejian_CASFilters</v>
       </c>
-      <c r="C381" s="18" t="s">
+      <c r="C381" s="19" t="s">
         <v>6438</v>
       </c>
-      <c r="D381" s="18" t="s">
+      <c r="D381" s="19" t="s">
         <v>6439</v>
       </c>
-      <c r="E381" s="18" t="s">
+      <c r="E381" s="19" t="s">
         <v>4549</v>
       </c>
-      <c r="F381" s="18" t="s">
+      <c r="F381" s="19" t="s">
         <v>5624</v>
       </c>
-      <c r="G381" s="15" t="s">
+      <c r="G381" s="16" t="s">
         <v>6376</v>
       </c>
     </row>
@@ -68875,32 +68879,32 @@
       <c r="K439" s="1"/>
     </row>
     <row r="440" spans="1:11">
-      <c r="A440" s="22" t="s">
+      <c r="A440" s="23" t="s">
         <v>6626</v>
       </c>
-      <c r="B440" s="22" t="str">
+      <c r="B440" s="23" t="str">
         <f>SUBSTITUTE(TRIM(D440)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C440)," ","")</f>
         <v>Simsiboy_MatteReplacement</v>
       </c>
-      <c r="C440" s="22" t="s">
+      <c r="C440" s="23" t="s">
         <v>6625</v>
       </c>
-      <c r="D440" s="22" t="s">
+      <c r="D440" s="23" t="s">
         <v>6126</v>
       </c>
-      <c r="E440" s="22" t="s">
+      <c r="E440" s="23" t="s">
         <v>4881</v>
       </c>
-      <c r="F440" s="22" t="s">
+      <c r="F440" s="23" t="s">
         <v>5278</v>
       </c>
-      <c r="G440" s="23" t="s">
+      <c r="G440" s="24" t="s">
         <v>6624</v>
       </c>
-      <c r="H440" s="22"/>
-      <c r="I440" s="22"/>
-      <c r="J440" s="22"/>
-      <c r="K440" s="22"/>
+      <c r="H440" s="23"/>
+      <c r="I440" s="23"/>
+      <c r="J440" s="23"/>
+      <c r="K440" s="23"/>
     </row>
     <row r="441" spans="1:11">
       <c r="A441" s="1" t="s">
@@ -69004,30 +69008,30 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="445" spans="1:11" s="26" customFormat="1">
-      <c r="A445" s="26" t="s">
+    <row r="445" spans="1:11" s="27" customFormat="1">
+      <c r="A445" s="27" t="s">
         <v>6629</v>
       </c>
-      <c r="B445" s="26" t="str">
+      <c r="B445" s="27" t="str">
         <f>SUBSTITUTE(TRIM(D445)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C445)," ","")</f>
         <v>Simsteries_InstantBusinessCashRegister</v>
       </c>
-      <c r="C445" s="26" t="s">
+      <c r="C445" s="27" t="s">
         <v>6474</v>
       </c>
-      <c r="D445" s="26" t="s">
+      <c r="D445" s="27" t="s">
         <v>6475</v>
       </c>
-      <c r="E445" s="26" t="s">
+      <c r="E445" s="27" t="s">
         <v>4552</v>
       </c>
-      <c r="F445" s="26" t="s">
+      <c r="F445" s="27" t="s">
         <v>3460</v>
       </c>
-      <c r="G445" s="28" t="s">
+      <c r="G445" s="29" t="s">
         <v>6473</v>
       </c>
-      <c r="H445" s="27" t="s">
+      <c r="H445" s="28" t="s">
         <v>6472</v>
       </c>
     </row>
@@ -69051,10 +69055,10 @@
       <c r="F446" s="14" t="s">
         <v>4534</v>
       </c>
-      <c r="G446" s="17" t="s">
+      <c r="G446" s="18" t="s">
         <v>5505</v>
       </c>
-      <c r="H446" s="17" t="s">
+      <c r="H446" s="18" t="s">
         <v>5506</v>
       </c>
       <c r="I446" s="14"/>
@@ -69135,8 +69139,11 @@
       <c r="F449" s="1" t="s">
         <v>4540</v>
       </c>
-      <c r="G449" s="1" t="s">
+      <c r="G449" s="15" t="s">
         <v>6130</v>
+      </c>
+      <c r="H449" s="1" t="s">
+        <v>6674</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -69717,13 +69724,13 @@
       <c r="D472" s="14" t="s">
         <v>6155</v>
       </c>
-      <c r="E472" s="24" t="s">
+      <c r="E472" s="25" t="s">
         <v>4549</v>
       </c>
-      <c r="F472" s="24" t="s">
+      <c r="F472" s="25" t="s">
         <v>4532</v>
       </c>
-      <c r="G472" s="17" t="s">
+      <c r="G472" s="18" t="s">
         <v>6154</v>
       </c>
       <c r="H472" s="14"/>
@@ -69756,32 +69763,32 @@
       </c>
     </row>
     <row r="474" spans="1:11">
-      <c r="A474" s="22" t="s">
+      <c r="A474" s="23" t="s">
         <v>6622</v>
       </c>
-      <c r="B474" s="22" t="str">
+      <c r="B474" s="23" t="str">
         <f>SUBSTITUTE(TRIM(D474)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C474)," ","")</f>
         <v>Tiasha_CCWrenchOverride</v>
       </c>
-      <c r="C474" s="22" t="s">
+      <c r="C474" s="23" t="s">
         <v>6164</v>
       </c>
-      <c r="D474" s="22" t="s">
+      <c r="D474" s="23" t="s">
         <v>6165</v>
       </c>
-      <c r="E474" s="22" t="s">
+      <c r="E474" s="23" t="s">
         <v>4881</v>
       </c>
-      <c r="F474" s="22" t="s">
+      <c r="F474" s="23" t="s">
         <v>5772</v>
       </c>
-      <c r="G474" s="29" t="s">
+      <c r="G474" s="30" t="s">
         <v>6166</v>
       </c>
-      <c r="H474" s="22"/>
-      <c r="I474" s="22"/>
-      <c r="J474" s="22"/>
-      <c r="K474" s="22"/>
+      <c r="H474" s="23"/>
+      <c r="I474" s="23"/>
+      <c r="J474" s="23"/>
+      <c r="K474" s="23"/>
     </row>
     <row r="475" spans="1:11">
       <c r="A475" s="1" t="s">
@@ -70079,10 +70086,10 @@
       <c r="D486" s="1" t="s">
         <v>5551</v>
       </c>
-      <c r="E486" s="25" t="s">
+      <c r="E486" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F486" s="25" t="s">
+      <c r="F486" s="26" t="s">
         <v>4886</v>
       </c>
       <c r="G486" s="1" t="s">
@@ -70103,10 +70110,10 @@
       <c r="D487" s="1" t="s">
         <v>5551</v>
       </c>
-      <c r="E487" s="25" t="s">
+      <c r="E487" s="26" t="s">
         <v>4882</v>
       </c>
-      <c r="F487" s="25" t="s">
+      <c r="F487" s="26" t="s">
         <v>6331</v>
       </c>
       <c r="G487" s="1" t="s">
@@ -70529,10 +70536,10 @@
       <c r="D503" s="1" t="s">
         <v>5587</v>
       </c>
-      <c r="E503" s="25" t="s">
+      <c r="E503" s="26" t="s">
         <v>4549</v>
       </c>
-      <c r="F503" s="25" t="s">
+      <c r="F503" s="26" t="s">
         <v>4532</v>
       </c>
       <c r="G503" s="1" t="s">
@@ -71662,7 +71669,7 @@
       <c r="C549" s="14" t="s">
         <v>6303</v>
       </c>
-      <c r="D549" s="16" t="s">
+      <c r="D549" s="17" t="s">
         <v>6296</v>
       </c>
       <c r="E549" s="14" t="s">
@@ -72683,34 +72690,34 @@
       </c>
     </row>
     <row r="589" spans="1:11">
-      <c r="A589" s="22" t="s">
+      <c r="A589" s="23" t="s">
         <v>5609</v>
       </c>
-      <c r="B589" s="22" t="str">
+      <c r="B589" s="23" t="str">
         <f>SUBSTITUTE(TRIM(D589)," ","")&amp;"_"&amp;SUBSTITUTE(TRIM(C589)," ","")</f>
         <v>zerbu_SpawnRefresh</v>
       </c>
-      <c r="C589" s="22" t="s">
+      <c r="C589" s="23" t="s">
         <v>5015</v>
       </c>
-      <c r="D589" s="22" t="s">
+      <c r="D589" s="23" t="s">
         <v>5010</v>
       </c>
-      <c r="E589" s="22" t="s">
+      <c r="E589" s="23" t="s">
         <v>4550</v>
       </c>
-      <c r="F589" s="22" t="s">
+      <c r="F589" s="23" t="s">
         <v>5016</v>
       </c>
-      <c r="G589" s="29" t="s">
+      <c r="G589" s="30" t="s">
         <v>5014</v>
       </c>
-      <c r="H589" s="29" t="s">
+      <c r="H589" s="30" t="s">
         <v>5013</v>
       </c>
-      <c r="I589" s="22"/>
-      <c r="J589" s="22"/>
-      <c r="K589" s="22"/>
+      <c r="I589" s="23"/>
+      <c r="J589" s="23"/>
+      <c r="K589" s="23"/>
     </row>
     <row r="590" spans="1:11">
       <c r="A590" s="1" t="s">
@@ -73076,11 +73083,12 @@
     <hyperlink ref="G82" r:id="rId220" xr:uid="{8D7E2F37-4A88-9849-A062-5A4717B58BB2}"/>
     <hyperlink ref="H50" r:id="rId221" xr:uid="{B17A26B3-5BA7-D049-85D4-9F48ABEE77A4}"/>
     <hyperlink ref="H29" r:id="rId222" xr:uid="{177CC75E-324E-794B-BEA5-887B97B797DB}"/>
+    <hyperlink ref="G449" r:id="rId223" xr:uid="{6DBCFD64-6857-4640-B5A1-0DDA047D5F3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId223"/>
+    <tablePart r:id="rId224"/>
   </tableParts>
 </worksheet>
 </file>
